--- a/output/2025/rosters-post-draft-2025-ffl.xlsx
+++ b/output/2025/rosters-post-draft-2025-ffl.xlsx
@@ -189,7 +189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1344,6 +1344,13 @@
     <row r="26"/>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>Column order is the 2025 draft order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Data retrieved Feb 15, 2026, 10:00 PM PT</t>
         </is>

--- a/output/2025/rosters-post-draft-2025-ffl.xlsx
+++ b/output/2025/rosters-post-draft-2025-ffl.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>South Town FF</t>
+          <t>South Town Freedom Fighters</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">

--- a/output/2025/rosters-post-draft-2025-ffl.xlsx
+++ b/output/2025/rosters-post-draft-2025-ffl.xlsx
@@ -189,65 +189,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="11" width="26" customWidth="1"/>
+    <col min="1" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Easton Evil Empire</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Easton Evil Empire</t>
+          <t>Riverstone Stoners</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Riverstone Stoners</t>
+          <t>Vancouver Moose Drool</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Vancouver Moose Drool</t>
+          <t>Visalia Viagra Vipers</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Visalia Viagra Vipers</t>
+          <t>Lemoore Liberators</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Lemoore Liberators</t>
+          <t>Dinkey Creek Dirt Clods</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Dinkey Creek Dirt Clods</t>
+          <t>Sanger Squatty Pottys</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Sanger Squatty Pottys</t>
+          <t>South Town Freedom Fighters</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>South Town Freedom Fighters</t>
+          <t>Clovis Jets</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Clovis Jets</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Kingsburg Killaz</t>
         </is>
@@ -256,7 +250,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>TIER 1</t>
+          <t>TIER 1 — Drafted Rounds 1–5</t>
         </is>
       </c>
       <c r="B2" s="10"/>
@@ -268,314 +262,283 @@
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
       <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Daniels, Jayden WAS QB</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Daniels, Jayden WAS QB</t>
+          <t>Jackson, Lamar BAL QB</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Jackson, Lamar BAL QB</t>
+          <t>Allen, Josh BUF QB</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Allen, Josh BUF QB</t>
+          <t>Hurts, Jalen PHI QB</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Hurts, Jalen PHI QB</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
           <t>Burrow, Joe CIN QB</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Robinson, Bijan ATL RB</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Chase, Ja'Marr CIN WR</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Barkley, Saquon PHI RB</t>
         </is>
       </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Jefferson, Justin MIN WR</t>
+        </is>
+      </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Jefferson, Justin MIN WR</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
           <t>Lamb, CeeDee DAL WR</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Collins, Nico HOU WR</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Collins, Nico HOU WR</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
           <t>Nabers, Malik NYG WR</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>McBride, Trey ARI TE</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Henry, Derrick BAL RB</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>St. Brown, Amon-Ra DET WR</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Bowers, Brock LV TE</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Mahomes, Patrick KC QB</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>McCaffrey, Christian SF RB</t>
+        </is>
+      </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>McCaffrey, Christian SF RB</t>
+          <t>Jeanty, Ashton LV RB</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Jeanty, Ashton LV RB</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
           <t>Gibbs, Jahmyr DET RB</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Thomas, Brian JAX WR</t>
         </is>
       </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Taylor, Jonathan IND RB</t>
+        </is>
+      </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Taylor, Jonathan IND RB</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
           <t>Irving, Bucky TB RB</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Nacua, Puka LAR WR</t>
         </is>
       </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Mayfield, Baker TB QB</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Mayfield, Baker TB QB</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
           <t>Nix, Bo DEN QB</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Cook, James BUF RB</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>London, Drake ATL WR</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Hampton, Omarion LAC RB</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>McConkey, Ladd LAC WR</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>4a</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Smith-Njigba, Jaxon SEA WR</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Smith-Njigba, Jaxon SEA WR</t>
+          <t>Wilson, Garrett NYJ WR</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Wilson, Garrett NYJ WR</t>
-        </is>
-      </c>
-      <c r="D6" s="2"/>
+          <t>Adams, Davante LAR WR</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Williams, Kyren LAR RB</t>
+        </is>
+      </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Williams, Kyren LAR RB</t>
+          <t>Achane, De'Von MIA RB</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Achane, De'Von MIA RB</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
           <t>Jacobs, Josh GB RB</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Kittle, George SF TE</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Stroud, C.J. HOU QB</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Brown, A.J. PHI WR</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>Brown, Chase CIN RB</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>4b</t>
-        </is>
-      </c>
-      <c r="B7" s="2"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Henderson, TreVeyon NE RB</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Higgins, Tee CIN WR</t>
+        </is>
+      </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Evans, Mike TB WR</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Harrison, Marvin ARI WR</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Herbert, Justin LAC QB</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Hubbard, Chuba CAR RB</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Love, Jordan GB QB</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Walker, Kenneth SEA RB</t>
         </is>
       </c>
-      <c r="K7" s="2"/>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Metcalf, DK PIT WR</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Henderson, TreVeyon NE RB</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Higgins, Tee CIN WR</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Adams, Davante LAR WR</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Evans, Mike TB WR</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Harrison, Marvin ARI WR</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Herbert, Justin LAC QB</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Hubbard, Chuba CAR RB</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Love, Jordan GB QB</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Hill, Tyreek MIA WR</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>Metcalf, DK PIT WR</t>
-        </is>
-      </c>
+      <c r="J8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>TIER 2</t>
+          <t>TIER 2 — Drafted Rounds 6–10</t>
         </is>
       </c>
       <c r="B9" s="11"/>
@@ -587,314 +550,283 @@
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Conner, James ARI RB</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Purdy, Brock SF QB</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>McLaurin, Terry WAS WR</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Fields, Justin NYJ QB</t>
         </is>
       </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Swift, D'Andre CHI RB</t>
+        </is>
+      </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Swift, D'Andre CHI RB</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
           <t>Kamara, Alvin NO RB</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Goff, Jared DET QB</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Harvey, RJ DEN RB</t>
         </is>
       </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Murray, Kyler ARI QB</t>
+        </is>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Murray, Kyler ARI QB</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
           <t>Prescott, Dak DAL QB</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>7a</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>McCarthy, J.J. MIN QB</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Hall, Breece NYJ RB</t>
         </is>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Maye, Drake NE QB</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Pollard, Tony TEN RB</t>
         </is>
       </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Smith, DeVonta PHI WR</t>
+        </is>
+      </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Smith, DeVonta PHI WR</t>
+          <t>Worthy, Xavier KC WR</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Worthy, Xavier KC WR</t>
+          <t>McMillan, Tetairoa CAR WR</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>McMillan, Tetairoa CAR WR</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
           <t>Sutton, Courtland DEN WR</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Pacheco, Isiah KC RB</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>Williams, Caleb CHI QB</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>7b</t>
-        </is>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Williams, Jameson DET WR</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Waddle, Jaylen MIA WR</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Montgomery, David DET RB</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Moore, DJ CHI WR</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Hockenson, T.J. MIN TE</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Diggs, Stefon NE WR</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Flowers, Zay BAL WR</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Kelce, Travis KC TE</t>
+        </is>
+      </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>Kelce, Travis KC TE</t>
-        </is>
-      </c>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
+          <t>LaPorta, Sam DET TE</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Odunze, Rome CHI WR</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Williams, Jameson DET WR</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Waddle, Jaylen MIA WR</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Maye, Drake NE QB</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Moore, DJ CHI WR</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Hockenson, T.J. MIN TE</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Andrews, Mark BAL TE</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Jones, Aaron MIN RB</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Williams, Javonte DAL RB</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Pickens, George DAL WR</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Tracy, Tyrone NYG RB</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Charbonnet, Zach SEA RB</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Diggs, Stefon NE WR</t>
+          <t>Hunter, Travis JAX WR</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Flowers, Zay BAL WR</t>
+          <t>Ridley, Calvin TEN WR</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Ridley, Calvin TEN WR</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>LaPorta, Sam DET TE</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>Odunze, Rome CHI WR</t>
+          <t>Rice, Rashee KC WR</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Johnson, Kaleb PIT RB</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Andrews, Mark BAL TE</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Jones, Aaron MIN RB</t>
-        </is>
-      </c>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Egbuka, Emeka TB WR</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Meyers, Jakobi LV WR</t>
+        </is>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Montgomery, David DET RB</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Pickens, George DAL WR</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Tracy, Tyrone NYG RB</t>
+          <t>Dobbins, J.K. DEN RB</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Warren, Jaylen PIT RB</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Pearsall, Ricky SF WR</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Charbonnet, Zach SEA RB</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>Hunter, Travis JAX WR</t>
+          <t>Etienne, Travis JAX RB</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Mixon, Joe HOU RB</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Mixon, Joe HOU RB</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>Rice, Rashee KC WR</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Johnson, Kaleb PIT RB</t>
+          <t>Judkins, Quinshon CLE RB</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Warren, Tyler IND TE</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Egbuka, Emeka TB WR</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Meyers, Jakobi LV WR</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Williams, Javonte DAL RB</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Dobbins, J.K. DEN RB</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Warren, Jaylen PIT RB</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Pearsall, Ricky SF WR</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Etienne, Travis JAX RB</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Samuel, Deebo WAS WR</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>Judkins, Quinshon CLE RB</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>Warren, Tyler IND TE</t>
-        </is>
-      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>TIER 3</t>
+          <t>TIER 3 — Drafted Rounds 11+</t>
         </is>
       </c>
       <c r="B16" s="12"/>
@@ -906,440 +838,394 @@
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Lawrence, Trevor JAX QB</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Engram, Evan DEN TE</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Jennings, Jauan SF WR</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Njoku, David CLE TE</t>
         </is>
       </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Penix, Michael ATL QB</t>
+        </is>
+      </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Penix, Michael ATL QB</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
           <t>Ward, Cam TEN QB</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Robinson, Brian SF RB</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Jeudy, Jerry CLE WR</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>Tagovailoa, Tua MIA QB</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>Skattebo, Cam NYG RB</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Addison, Jordan MIN WR</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Smith, Geno LV QB</t>
         </is>
       </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Golden, Matthew GB WR</t>
+        </is>
+      </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Golden, Matthew GB WR</t>
+          <t>Kupp, Cooper SEA WR</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Kupp, Cooper SEA WR</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
           <t>Shakir, Khalil BUF WR</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>Croskey-Merritt, Jacory WAS RB</t>
         </is>
       </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Stafford, Matthew LAR QB</t>
+        </is>
+      </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Stafford, Matthew LAR QB</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
           <t>Darnold, Sam SEA QB</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>Olave, Chris NO WR</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>Mason, Jordan MIN RB</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>13</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Tuten, Bhayshul JAX RB</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Tuten, Bhayshul JAX RB</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
           <t>Stevenson, Rhamondre NE RB</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Godwin, Chris TB WR</t>
         </is>
       </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Ekeler, Austin WAS RB</t>
+        </is>
+      </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Ekeler, Austin WAS RB</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
           <t>Bigsby, Tank JAX RB</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Loveland, Colston CHI TE</t>
         </is>
       </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Coleman, Keon BUF WR</t>
+        </is>
+      </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>Coleman, Keon BUF WR</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
           <t>Aiyuk, Brandon SF WR</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Allen, Braelon NYJ RB</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Higgins, Jayden HOU WR</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>14</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Benson, Trey ARI RB</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Benson, Trey ARI RB</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
           <t>Chubb, Nick HOU RB</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Eagles, Philadelphia PHI DEF</t>
         </is>
       </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Pittman, Michael IND WR</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Pittman, Michael IND WR</t>
+          <t>Reed, Jayden GB WR</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Reed, Jayden GB WR</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
           <t>Kirk, Christian HOU WR</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>White, Rachaad TB RB</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>Kraft, Tucker GB TE</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>Dart, Jaxson NYG QB</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Burden, Luther CHI WR</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Young, Bryce CAR QB</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Allgeier, Tyler ATL RB</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Pitts, Kyle ATL TE</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>Broncos, Denver DEN DEF</t>
         </is>
       </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Rodgers, Aaron PIT QB</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Rodgers, Aaron PIT QB</t>
+          <t>Richardson, Anthony IND QB</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Richardson, Anthony IND QB</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
           <t>Jones, Daniel IND QB</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>Chiefs, Kansas City KC DEF</t>
         </is>
       </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>Bates, Jake DET K</t>
+        </is>
+      </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>Bates, Jake DET K</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
           <t>Aubrey, Brandon DAL K</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Vikings, Minnesota MIN DEF</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Butker, Harrison KC K</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Downs, Josh IND WR</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Dicker, Cameron LAC K</t>
         </is>
       </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Ravens, Baltimore BAL DEF</t>
+        </is>
+      </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Ravens, Baltimore BAL DEF</t>
+          <t>49ers, San Francisco SF DEF</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>49ers, San Francisco SF DEF</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
           <t>Bills, Buffalo BUF DEF</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Karty, Joshua LAR K</t>
         </is>
       </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Texans, Houston HOU DEF</t>
+        </is>
+      </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>Texans, Houston HOU DEF</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
           <t>Steelers, Pittsburgh PIT DEF</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>17a</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Boswell, Chris PIT K</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Lions, Detroit DET DEF</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Lutz, Wil DEN K</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Wilson, Russell NYG QB</t>
         </is>
       </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>Koo, Younghoe ATL K</t>
+        </is>
+      </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>Koo, Younghoe ATL K</t>
+          <t>Bass, Tyler BUF K</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Bass, Tyler BUF K</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
           <t>McLaughlin, Chase TB K</t>
         </is>
       </c>
+      <c r="H23" s="2"/>
       <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="6" t="inlineStr">
+      <c r="J23" s="6" t="inlineStr">
         <is>
           <t>Kincaid, Dalton BUF TE</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>17b</t>
-        </is>
-      </c>
+      <c r="A24" s="2"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Mooney, Darnell ATL WR</t>
         </is>
       </c>
+      <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>17c</t>
-        </is>
-      </c>
+      <c r="A25" s="2"/>
       <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Spears, Tyjae TEN RB</t>
         </is>
       </c>
+      <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
     </row>
     <row r="26"/>
     <row r="27">
@@ -1358,9 +1244,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A16:J16"/>
   </mergeCells>
 </worksheet>
 </file>
